--- a/artfynd/A 8303-2024 artfynd.xlsx
+++ b/artfynd/A 8303-2024 artfynd.xlsx
@@ -946,7 +946,7 @@
         <v>117982722</v>
       </c>
       <c r="B4" t="n">
-        <v>103821</v>
+        <v>103823</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8303-2024 artfynd.xlsx
+++ b/artfynd/A 8303-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2374542</v>
+        <v>598172</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219955</v>
+        <v>1560</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>174</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545961.9638697139</v>
+        <v>545972</v>
       </c>
       <c r="R2" t="n">
-        <v>6323106.027135794</v>
+        <v>6323096</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +757,9 @@
           <t>2012-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -793,7 +778,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vändplan</t>
+          <t>Grusvägsslänt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,45 +796,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15283633</v>
+        <v>117982722</v>
       </c>
       <c r="B3" t="n">
-        <v>44175</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102421</v>
+        <v>1560</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåttergubbemal</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Digitivalva arnicella</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(von Heyden, 1863)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>mina</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -857,17 +843,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1000 m S Tämshult, Sm</t>
+          <t>Djuphultsvägen, Grytsjön, Kråksmåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545961.9638697139</v>
+        <v>545973</v>
       </c>
       <c r="R3" t="n">
-        <v>6323106.027135794</v>
+        <v>6323103</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,27 +877,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-07-28</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-07-28</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ledningsgata</t>
+          <t>längs med vägen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,38 +906,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vändplan</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Lager</t>
+          <t>Katharina Ahlert</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ekologa /Jonas Wäglind</t>
+          <t>Katharina Ahlert</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117982722</v>
+        <v>15283631</v>
       </c>
       <c r="B4" t="n">
-        <v>103832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>26894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,35 +936,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1560</v>
+        <v>101766</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Spindelörtskinnbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Canthophorus impressus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Horváth, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -995,17 +975,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djuphultsvägen, Grytsjön, Kråksmåla, Sm</t>
+          <t>1000 m S Tämshult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545973</v>
+        <v>545972</v>
       </c>
       <c r="R4" t="n">
-        <v>6323103</v>
+        <v>6323096</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,27 +1009,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2012-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07:00</t>
+          <t>2012-07-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>längs med vägen</t>
+          <t>Ledningsgata</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,22 +1028,147 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Längs grusväg</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Katharina Ahlert</t>
+          <t>Helena Lager</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Katharina Ahlert</t>
+          <t>Ekologa /Jonas Wäglind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2374538</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>1000 m S Tämshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545962</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6323106</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-07-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-07-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ledningsgata</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vändplan</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helena Lager</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8303-2024 artfynd.xlsx
+++ b/artfynd/A 8303-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/598172</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117982722</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15283631</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,8 +1189,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2374538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>